--- a/WG Member Contact 2025 web.xlsx
+++ b/WG Member Contact 2025 web.xlsx
@@ -1337,7 +1337,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>University of Minnesota</t>
+          <t>University of Wisconsin–Madison</t>
         </is>
       </c>
     </row>
